--- a/sample_data/Order.xlsx
+++ b/sample_data/Order.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>ExpectedQty</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -454,8 +459,15 @@
           <t>Delhi</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>100</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Apr-2026</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -474,8 +486,15 @@
           <t>Delhi</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>80</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Jun-2026</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -494,8 +513,15 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>60</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sep-2026</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -514,8 +540,15 @@
           <t>Delhi</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>50</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dec-2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
